--- a/excel/butterScaler/butterScaler23-Section07.xlsx
+++ b/excel/butterScaler/butterScaler23-Section07.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10331"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{693D597F-18E6-A141-AB50-FB350C947A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD07C8C-FF27-2C4A-B2BC-B3C0B632C638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{ABEA9CE0-9C8C-3547-94E6-FE5BD0101E05}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="48">
   <si>
     <t>ActionName</t>
   </si>
@@ -161,13 +161,16 @@
   </si>
   <si>
     <t>结束</t>
+  </si>
+  <si>
+    <t>StepActionName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -302,6 +305,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -484,7 +493,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -599,6 +608,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -644,8 +668,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1021,999 +1049,1005 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B731C6-0B47-1C4C-876C-9E0CF0BB38C4}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="b">
+      <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="b">
+      <c r="I7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>21</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>21</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" t="b">
+      <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>22</v>
       </c>
-      <c r="H12" t="b">
+      <c r="I12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>24</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>25</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>25</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>27</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>27</v>
       </c>
-      <c r="F16" t="b">
+      <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>28</v>
       </c>
-      <c r="H16" t="b">
+      <c r="I16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
         <v>30</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18">
         <v>6</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>31</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>29</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
         <v>15</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>32</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="b">
+      <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>33</v>
       </c>
-      <c r="H22" t="b">
+      <c r="I22" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>33</v>
       </c>
       <c r="B23">
         <v>8</v>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>34</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>35</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24">
         <v>8</v>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
         <v>36</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>37</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>34</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>35</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26">
         <v>8</v>
       </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>37</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
       <c r="B27">
         <v>8</v>
       </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
         <v>34</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>35</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28">
         <v>8</v>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
         <v>36</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>37</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29">
         <v>8</v>
       </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
         <v>34</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>35</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
         <v>36</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>37</v>
       </c>
-      <c r="F30" t="b">
+      <c r="G30" t="b">
         <v>1</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>38</v>
       </c>
-      <c r="H30" t="b">
+      <c r="I30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>23</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
         <v>24</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>39</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>23</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
         <v>24</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>39</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>23</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
         <v>40</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>41</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>23</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
         <v>40</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>41</v>
       </c>
-      <c r="F34" t="b">
+      <c r="G34" t="b">
         <v>1</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>42</v>
       </c>
-      <c r="H34" t="b">
+      <c r="I34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>29</v>
       </c>
       <c r="B35">
         <v>8</v>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
         <v>30</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>43</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>29</v>
       </c>
       <c r="B36">
         <v>8</v>
       </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
         <v>30</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>43</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>29</v>
       </c>
       <c r="B37">
         <v>8</v>
       </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
         <v>30</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>43</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>29</v>
       </c>
       <c r="B38">
         <v>8</v>
       </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>45</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>29</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
         <v>44</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>45</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>29</v>
       </c>
       <c r="B40">
         <v>8</v>
       </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>45</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>29</v>
       </c>
       <c r="B41">
         <v>8</v>
       </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
         <v>44</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>45</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>29</v>
       </c>
       <c r="B42">
         <v>8</v>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
         <v>44</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>45</v>
       </c>
-      <c r="F42" t="b">
+      <c r="G42" t="b">
         <v>1</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>46</v>
       </c>
-      <c r="H42" t="b">
+      <c r="I42" t="b">
         <v>1</v>
       </c>
     </row>
